--- a/outputs/sesi_relatorio_qualidade.xlsx
+++ b/outputs/sesi_relatorio_qualidade.xlsx
@@ -501,7 +501,7 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>Execução Orçamentária (SESI - DN - 2025)</t>
+          <t>Execução Orçamentária (SESI - DN - 2024)</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -511,7 +511,7 @@
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>https://sorsdn.sistemaindustria.com.br/api/Transparencia/Get?entidade=SESI&amp;regional=DN&amp;ano=2025</t>
+          <t>https://sorsdn.sistemaindustria.com.br/api/Transparencia/Get?entidade=SESI&amp;regional=DN&amp;ano=2024</t>
         </is>
       </c>
       <c r="G2" t="n">
@@ -537,7 +537,7 @@
       </c>
       <c r="L2" t="inlineStr">
         <is>
-          <t>2026-08-13 17:09:35</t>
+          <t>2026-08-17 14:51:12</t>
         </is>
       </c>
     </row>
@@ -557,7 +557,7 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>Saldo Exercício Anterior (SESI - DN - 2025)</t>
+          <t>Saldo Exercício Anterior (SESI - DN - 2024)</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -567,7 +567,7 @@
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>https://sorsdn.sistemaindustria.com.br/api/Transparencia/GetSaldoExercicioAnterior?entidade=SESI&amp;regional=DN&amp;ano=2025</t>
+          <t>https://sorsdn.sistemaindustria.com.br/api/Transparencia/GetSaldoExercicioAnterior?entidade=SESI&amp;regional=DN&amp;ano=2024</t>
         </is>
       </c>
       <c r="G3" t="n">
@@ -593,7 +593,7 @@
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>2026-08-13 17:09:35</t>
+          <t>2026-08-17 14:51:12</t>
         </is>
       </c>
     </row>
@@ -613,7 +613,7 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>Previsão Orçamentária (SESI - 2025)</t>
+          <t>Previsão Orçamentária (SESI - 2024)</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
@@ -623,7 +623,7 @@
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>https://sorsdn.sistemaindustria.com.br/api/Transparencia/GetPrevisaoOrcamentaria?entidade=SESI&amp;ano=2025</t>
+          <t>https://sorsdn.sistemaindustria.com.br/api/Transparencia/GetPrevisaoOrcamentaria?entidade=SESI&amp;ano=2024</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -649,7 +649,7 @@
       </c>
       <c r="L4" t="inlineStr">
         <is>
-          <t>2026-08-13 17:09:35</t>
+          <t>2026-08-17 14:51:12</t>
         </is>
       </c>
     </row>
@@ -669,7 +669,7 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>Rateio de Despesas (SESI - DN - 2025)</t>
+          <t>Rateio de Despesas (SESI - DN - 2024)</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -679,7 +679,7 @@
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>https://sorsdn.sistemaindustria.com.br/api/Transparencia/GetRateio?entidade=SESI&amp;regional=DN&amp;ano=2025</t>
+          <t>https://sorsdn.sistemaindustria.com.br/api/Transparencia/GetRateio?entidade=SESI&amp;regional=DN&amp;ano=2024</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -705,7 +705,7 @@
       </c>
       <c r="L5" t="inlineStr">
         <is>
-          <t>2026-08-13 17:09:35</t>
+          <t>2026-08-17 14:51:12</t>
         </is>
       </c>
     </row>
@@ -725,7 +725,7 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>Despesas por Licitação (SESI - DN - 2025)</t>
+          <t>Despesas por Licitação (SESI - DN - 2024)</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
@@ -735,7 +735,7 @@
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>https://sorsdn.sistemaindustria.com.br/api/Transparencia/GetLicitacao?entidade=SESI&amp;regional=DN&amp;ano=2025</t>
+          <t>https://sorsdn.sistemaindustria.com.br/api/Transparencia/GetLicitacao?entidade=SESI&amp;regional=DN&amp;ano=2024</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -761,7 +761,7 @@
       </c>
       <c r="L6" t="inlineStr">
         <is>
-          <t>2026-08-13 17:09:35</t>
+          <t>2026-08-17 14:51:12</t>
         </is>
       </c>
     </row>
@@ -781,7 +781,7 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>Bens Imóveis (SESI - DN - 2025)</t>
+          <t>Bens Imóveis (SESI - DN - 2024)</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -791,7 +791,7 @@
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>https://sorsdn.sistemaindustria.com.br/api/Transparencia/GetBensImoveis?entidade=SESI&amp;regional=DN&amp;ano=2025</t>
+          <t>https://sorsdn.sistemaindustria.com.br/api/Transparencia/GetBensImoveis?entidade=SESI&amp;regional=DN&amp;ano=2024</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -817,7 +817,7 @@
       </c>
       <c r="L7" t="inlineStr">
         <is>
-          <t>2026-08-13 17:09:35</t>
+          <t>2026-08-17 14:51:12</t>
         </is>
       </c>
     </row>
@@ -933,7 +933,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>22/01/2026 12:31</t>
+          <t>27/01/2025 09:55</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -953,7 +953,7 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Valores Aprovados no Plano de Ação Retificado 2025</t>
+          <t>Valores Aprovados no Plano de Ação Retificado 2024</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
@@ -971,22 +971,22 @@
         </is>
       </c>
       <c r="J2" t="n">
-        <v>2007776307</v>
+        <v>1753191244.86</v>
       </c>
       <c r="K2" t="n">
-        <v>1981389324.71</v>
+        <v>1826995606.21</v>
       </c>
       <c r="L2" t="n">
-        <v>98.7</v>
+        <v>104.2</v>
       </c>
       <c r="M2" t="n">
-        <v>75</v>
+        <v>79.8</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>22/01/2026 12:31</t>
+          <t>27/01/2025 09:55</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -1006,7 +1006,7 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Valores Aprovados no Plano de Ação Retificado 2025</t>
+          <t>Valores Aprovados no Plano de Ação Retificado 2024</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
@@ -1028,22 +1028,22 @@
         </is>
       </c>
       <c r="J3" t="n">
-        <v>941682277.03</v>
+        <v>849593679.49</v>
       </c>
       <c r="K3" t="n">
-        <v>940984334.8099999</v>
+        <v>870230073.02</v>
       </c>
       <c r="L3" t="n">
-        <v>99.90000000000001</v>
+        <v>102.4</v>
       </c>
       <c r="M3" t="n">
-        <v>35.2</v>
+        <v>38.7</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>22/01/2026 12:31</t>
+          <t>27/01/2025 09:55</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -1063,7 +1063,7 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Valores Aprovados no Plano de Ação Retificado 2025</t>
+          <t>Valores Aprovados no Plano de Ação Retificado 2024</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
@@ -1085,22 +1085,22 @@
         </is>
       </c>
       <c r="J4" t="n">
-        <v>1066094029.97</v>
+        <v>903597565.37</v>
       </c>
       <c r="K4" t="n">
-        <v>1040404989.9</v>
+        <v>956765533.1900001</v>
       </c>
       <c r="L4" t="n">
-        <v>97.59999999999999</v>
+        <v>105.9</v>
       </c>
       <c r="M4" t="n">
-        <v>39.8</v>
+        <v>41.1</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>22/01/2026 12:31</t>
+          <t>27/01/2025 09:55</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -1120,7 +1120,7 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Valores Aprovados no Plano de Ação Retificado 2025</t>
+          <t>Valores Aprovados no Plano de Ação Retificado 2024</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
@@ -1157,7 +1157,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>22/01/2026 12:31</t>
+          <t>27/01/2025 09:55</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -1177,7 +1177,7 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Valores Aprovados no Plano de Ação Retificado 2025</t>
+          <t>Valores Aprovados no Plano de Ação Retificado 2024</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
@@ -1214,7 +1214,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>22/01/2026 12:31</t>
+          <t>27/01/2025 09:55</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -1234,7 +1234,7 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Valores Aprovados no Plano de Ação Retificado 2025</t>
+          <t>Valores Aprovados no Plano de Ação Retificado 2024</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
@@ -1271,7 +1271,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>22/01/2026 12:31</t>
+          <t>27/01/2025 09:55</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1291,7 +1291,7 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Valores Aprovados no Plano de Ação Retificado 2025</t>
+          <t>Valores Aprovados no Plano de Ação Retificado 2024</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
@@ -1328,7 +1328,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>22/01/2026 12:31</t>
+          <t>27/01/2025 09:55</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1348,7 +1348,7 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Valores Aprovados no Plano de Ação Retificado 2025</t>
+          <t>Valores Aprovados no Plano de Ação Retificado 2024</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
@@ -1385,7 +1385,7 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>22/01/2026 12:31</t>
+          <t>27/01/2025 09:55</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1405,7 +1405,7 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Valores Aprovados no Plano de Ação Retificado 2025</t>
+          <t>Valores Aprovados no Plano de Ação Retificado 2024</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
@@ -1423,22 +1423,22 @@
         </is>
       </c>
       <c r="J10" t="n">
-        <v>491436657.69</v>
+        <v>339099541.22</v>
       </c>
       <c r="K10" t="n">
-        <v>533046326.99</v>
+        <v>340053613.88</v>
       </c>
       <c r="L10" t="n">
-        <v>108.5</v>
+        <v>100.3</v>
       </c>
       <c r="M10" t="n">
-        <v>18.4</v>
+        <v>15.4</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>22/01/2026 12:31</t>
+          <t>27/01/2025 09:55</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1458,7 +1458,7 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Valores Aprovados no Plano de Ação Retificado 2025</t>
+          <t>Valores Aprovados no Plano de Ação Retificado 2024</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
@@ -1480,13 +1480,13 @@
         </is>
       </c>
       <c r="J11" t="n">
-        <v>544169</v>
+        <v>296912.84</v>
       </c>
       <c r="K11" t="n">
-        <v>223400</v>
+        <v>139290</v>
       </c>
       <c r="L11" t="n">
-        <v>41.1</v>
+        <v>46.9</v>
       </c>
       <c r="M11" t="n">
         <v>0</v>
@@ -1495,7 +1495,7 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>22/01/2026 12:31</t>
+          <t>27/01/2025 09:55</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1515,7 +1515,7 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Valores Aprovados no Plano de Ação Retificado 2025</t>
+          <t>Valores Aprovados no Plano de Ação Retificado 2024</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
@@ -1537,22 +1537,22 @@
         </is>
       </c>
       <c r="J12" t="n">
-        <v>490892488.69</v>
+        <v>338802628.38</v>
       </c>
       <c r="K12" t="n">
-        <v>532822926.99</v>
+        <v>339914323.88</v>
       </c>
       <c r="L12" t="n">
-        <v>108.5</v>
+        <v>100.3</v>
       </c>
       <c r="M12" t="n">
-        <v>18.3</v>
+        <v>15.4</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>22/01/2026 12:31</t>
+          <t>27/01/2025 09:55</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -1572,7 +1572,7 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Valores Aprovados no Plano de Ação Retificado 2025</t>
+          <t>Valores Aprovados no Plano de Ação Retificado 2024</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
@@ -1605,7 +1605,7 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>22/01/2026 12:31</t>
+          <t>27/01/2025 09:55</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1625,7 +1625,7 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Valores Aprovados no Plano de Ação Retificado 2025</t>
+          <t>Valores Aprovados no Plano de Ação Retificado 2024</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
@@ -1662,7 +1662,7 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>22/01/2026 12:31</t>
+          <t>27/01/2025 09:55</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1682,7 +1682,7 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Valores Aprovados no Plano de Ação Retificado 2025</t>
+          <t>Valores Aprovados no Plano de Ação Retificado 2024</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
@@ -1719,7 +1719,7 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>22/01/2026 12:31</t>
+          <t>27/01/2025 09:55</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1739,7 +1739,7 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Valores Aprovados no Plano de Ação Retificado 2025</t>
+          <t>Valores Aprovados no Plano de Ação Retificado 2024</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
@@ -1757,22 +1757,22 @@
         </is>
       </c>
       <c r="J16" t="n">
-        <v>82109768.09999999</v>
+        <v>18892957.9</v>
       </c>
       <c r="K16" t="n">
-        <v>26853338.18</v>
+        <v>28619437.54</v>
       </c>
       <c r="L16" t="n">
-        <v>32.7</v>
+        <v>151.5</v>
       </c>
       <c r="M16" t="n">
-        <v>3.1</v>
+        <v>0.9</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>22/01/2026 12:31</t>
+          <t>27/01/2025 09:55</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1792,7 +1792,7 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Valores Aprovados no Plano de Ação Retificado 2025</t>
+          <t>Valores Aprovados no Plano de Ação Retificado 2024</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
@@ -1814,22 +1814,22 @@
         </is>
       </c>
       <c r="J17" t="n">
-        <v>81603768.09999999</v>
+        <v>480000</v>
       </c>
       <c r="K17" t="n">
-        <v>312401.9</v>
+        <v>433103.26</v>
       </c>
       <c r="L17" t="n">
-        <v>0.4</v>
+        <v>90.2</v>
       </c>
       <c r="M17" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>22/01/2026 12:31</t>
+          <t>27/01/2025 09:55</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1849,7 +1849,7 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Valores Aprovados no Plano de Ação Retificado 2025</t>
+          <t>Valores Aprovados no Plano de Ação Retificado 2024</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
@@ -1886,7 +1886,7 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>22/01/2026 12:31</t>
+          <t>27/01/2025 09:55</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1906,7 +1906,7 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Valores Aprovados no Plano de Ação Retificado 2025</t>
+          <t>Valores Aprovados no Plano de Ação Retificado 2024</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
@@ -1931,7 +1931,7 @@
         <v>0</v>
       </c>
       <c r="K19" t="n">
-        <v>15591720.03</v>
+        <v>125400.5</v>
       </c>
       <c r="L19" t="n">
         <v>0</v>
@@ -1943,7 +1943,7 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>22/01/2026 12:31</t>
+          <t>27/01/2025 09:55</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1963,7 +1963,7 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Valores Aprovados no Plano de Ação Retificado 2025</t>
+          <t>Valores Aprovados no Plano de Ação Retificado 2024</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
@@ -1985,7 +1985,7 @@
         </is>
       </c>
       <c r="J20" t="n">
-        <v>0</v>
+        <v>581013.9</v>
       </c>
       <c r="K20" t="n">
         <v>0</v>
@@ -2000,7 +2000,7 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>22/01/2026 12:31</t>
+          <t>27/01/2025 09:55</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -2020,7 +2020,7 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Valores Aprovados no Plano de Ação Retificado 2025</t>
+          <t>Valores Aprovados no Plano de Ação Retificado 2024</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
@@ -2042,13 +2042,13 @@
         </is>
       </c>
       <c r="J21" t="n">
-        <v>65000</v>
+        <v>286570.22</v>
       </c>
       <c r="K21" t="n">
-        <v>147630.35</v>
+        <v>472552.15</v>
       </c>
       <c r="L21" t="n">
-        <v>227.1</v>
+        <v>164.9</v>
       </c>
       <c r="M21" t="n">
         <v>0</v>
@@ -2138,7 +2138,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>22/01/2026 12:31</t>
+          <t>27/01/2025 09:55</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -2191,7 +2191,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>22/01/2026 12:31</t>
+          <t>27/01/2025 09:55</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -2244,7 +2244,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>22/01/2026 12:31</t>
+          <t>27/01/2025 09:55</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -2297,7 +2297,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>22/01/2026 12:31</t>
+          <t>27/01/2025 09:55</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -2350,7 +2350,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>22/01/2026 12:31</t>
+          <t>27/01/2025 09:55</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -2403,7 +2403,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>22/01/2026 12:31</t>
+          <t>27/01/2025 09:55</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -2456,7 +2456,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>22/01/2026 12:31</t>
+          <t>27/01/2025 09:55</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -2509,7 +2509,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>22/01/2026 12:31</t>
+          <t>27/01/2025 09:55</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -2562,7 +2562,7 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>22/01/2026 12:31</t>
+          <t>27/01/2025 09:55</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -2615,7 +2615,7 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>22/01/2026 12:31</t>
+          <t>27/01/2025 09:55</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -2725,11 +2725,7 @@
           <t>Jan - Dez</t>
         </is>
       </c>
-      <c r="B2" t="inlineStr">
-        <is>
-          <t>O Conselho Nacional do Serviço Social da Indústria (SESI), em 28/07/2025, no uso de suas atribuições legais e regulamentares, resolveu aprovar o Plano de Ação e Orçamento Retificado do sistema SESI , para o exercício de 2025 (Resolução SESI/CN Nº 0052/2025).</t>
-        </is>
-      </c>
+      <c r="B2" t="inlineStr"/>
       <c r="C2" t="inlineStr">
         <is>
           <t>PREVORC_REC</t>
@@ -2752,7 +2748,7 @@
         </is>
       </c>
       <c r="H2" t="n">
-        <v>8031105228.05</v>
+        <v>7005567116.64</v>
       </c>
     </row>
     <row r="3">
@@ -2761,11 +2757,7 @@
           <t>Jan - Dez</t>
         </is>
       </c>
-      <c r="B3" t="inlineStr">
-        <is>
-          <t>O Conselho Nacional do Serviço Social da Indústria (SESI), em 28/07/2025, no uso de suas atribuições legais e regulamentares, resolveu aprovar o Plano de Ação e Orçamento Retificado do sistema SESI , para o exercício de 2025 (Resolução SESI/CN Nº 0052/2025).</t>
-        </is>
-      </c>
+      <c r="B3" t="inlineStr"/>
       <c r="C3" t="inlineStr">
         <is>
           <t>PREVORC_REC</t>
@@ -2792,7 +2784,7 @@
         </is>
       </c>
       <c r="H3" t="n">
-        <v>3766729108.12</v>
+        <v>3391176855.57</v>
       </c>
     </row>
     <row r="4">
@@ -2801,11 +2793,7 @@
           <t>Jan - Dez</t>
         </is>
       </c>
-      <c r="B4" t="inlineStr">
-        <is>
-          <t>O Conselho Nacional do Serviço Social da Indústria (SESI), em 28/07/2025, no uso de suas atribuições legais e regulamentares, resolveu aprovar o Plano de Ação e Orçamento Retificado do sistema SESI , para o exercício de 2025 (Resolução SESI/CN Nº 0052/2025).</t>
-        </is>
-      </c>
+      <c r="B4" t="inlineStr"/>
       <c r="C4" t="inlineStr">
         <is>
           <t>PREVORC_REC</t>
@@ -2832,7 +2820,7 @@
         </is>
       </c>
       <c r="H4" t="n">
-        <v>4264376119.93</v>
+        <v>3614390261.07</v>
       </c>
     </row>
     <row r="5">
@@ -2841,11 +2829,7 @@
           <t>Jan - Dez</t>
         </is>
       </c>
-      <c r="B5" t="inlineStr">
-        <is>
-          <t>O Conselho Nacional do Serviço Social da Indústria (SESI), em 28/07/2025, no uso de suas atribuições legais e regulamentares, resolveu aprovar o Plano de Ação e Orçamento Retificado do sistema SESI , para o exercício de 2025 (Resolução SESI/CN Nº 0052/2025).</t>
-        </is>
-      </c>
+      <c r="B5" t="inlineStr"/>
       <c r="C5" t="inlineStr">
         <is>
           <t>PREVORC_REC</t>
@@ -2868,7 +2852,7 @@
         </is>
       </c>
       <c r="H5" t="n">
-        <v>100388815</v>
+        <v>87659562</v>
       </c>
     </row>
     <row r="6">
@@ -2877,11 +2861,7 @@
           <t>Jan - Dez</t>
         </is>
       </c>
-      <c r="B6" t="inlineStr">
-        <is>
-          <t>O Conselho Nacional do Serviço Social da Indústria (SESI), em 28/07/2025, no uso de suas atribuições legais e regulamentares, resolveu aprovar o Plano de Ação e Orçamento Retificado do sistema SESI , para o exercício de 2025 (Resolução SESI/CN Nº 0052/2025).</t>
-        </is>
-      </c>
+      <c r="B6" t="inlineStr"/>
       <c r="C6" t="inlineStr">
         <is>
           <t>PREVORC_REC</t>
@@ -2904,7 +2884,7 @@
         </is>
       </c>
       <c r="H6" t="n">
-        <v>38919637.99</v>
+        <v>33780272.33</v>
       </c>
     </row>
     <row r="7">
@@ -2913,11 +2893,7 @@
           <t>Jan - Dez</t>
         </is>
       </c>
-      <c r="B7" t="inlineStr">
-        <is>
-          <t>O Conselho Nacional do Serviço Social da Indústria (SESI), em 28/07/2025, no uso de suas atribuições legais e regulamentares, resolveu aprovar o Plano de Ação e Orçamento Retificado do sistema SESI , para o exercício de 2025 (Resolução SESI/CN Nº 0052/2025).</t>
-        </is>
-      </c>
+      <c r="B7" t="inlineStr"/>
       <c r="C7" t="inlineStr">
         <is>
           <t>PREVORC_REC</t>
@@ -2940,7 +2916,7 @@
         </is>
       </c>
       <c r="H7" t="n">
-        <v>1643883248.04</v>
+        <v>1083832927.63</v>
       </c>
     </row>
     <row r="8">
@@ -2949,11 +2925,7 @@
           <t>Jan - Dez</t>
         </is>
       </c>
-      <c r="B8" t="inlineStr">
-        <is>
-          <t>O Conselho Nacional do Serviço Social da Indústria (SESI), em 28/07/2025, no uso de suas atribuições legais e regulamentares, resolveu aprovar o Plano de Ação e Orçamento Retificado do sistema SESI , para o exercício de 2025 (Resolução SESI/CN Nº 0052/2025).</t>
-        </is>
-      </c>
+      <c r="B8" t="inlineStr"/>
       <c r="C8" t="inlineStr">
         <is>
           <t>PREVORC_REC</t>
@@ -2976,7 +2948,7 @@
         </is>
       </c>
       <c r="H8" t="n">
-        <v>357468663.85</v>
+        <v>320933248.56</v>
       </c>
     </row>
     <row r="9">
@@ -2985,11 +2957,7 @@
           <t>Jan - Dez</t>
         </is>
       </c>
-      <c r="B9" t="inlineStr">
-        <is>
-          <t>O Conselho Nacional do Serviço Social da Indústria (SESI), em 28/07/2025, no uso de suas atribuições legais e regulamentares, resolveu aprovar o Plano de Ação e Orçamento Retificado do sistema SESI , para o exercício de 2025 (Resolução SESI/CN Nº 0052/2025).</t>
-        </is>
-      </c>
+      <c r="B9" t="inlineStr"/>
       <c r="C9" t="inlineStr">
         <is>
           <t>PREVORC_REC</t>
@@ -3012,7 +2980,7 @@
         </is>
       </c>
       <c r="H9" t="n">
-        <v>480108063.89</v>
+        <v>390753696.41</v>
       </c>
     </row>
     <row r="10">
@@ -3021,11 +2989,7 @@
           <t>Jan - Dez</t>
         </is>
       </c>
-      <c r="B10" t="inlineStr">
-        <is>
-          <t>O Conselho Nacional do Serviço Social da Indústria (SESI), em 28/07/2025, no uso de suas atribuições legais e regulamentares, resolveu aprovar o Plano de Ação e Orçamento Retificado do sistema SESI , para o exercício de 2025 (Resolução SESI/CN Nº 0052/2025).</t>
-        </is>
-      </c>
+      <c r="B10" t="inlineStr"/>
       <c r="C10" t="inlineStr">
         <is>
           <t>PREVORC_REC</t>
@@ -3048,7 +3012,7 @@
         </is>
       </c>
       <c r="H10" t="n">
-        <v>6832031.2</v>
+        <v>5975998.5</v>
       </c>
     </row>
     <row r="11">
@@ -3057,11 +3021,7 @@
           <t>Jan - Dez</t>
         </is>
       </c>
-      <c r="B11" t="inlineStr">
-        <is>
-          <t>O Conselho Nacional do Serviço Social da Indústria (SESI), em 28/07/2025, no uso de suas atribuições legais e regulamentares, resolveu aprovar o Plano de Ação e Orçamento Retificado do sistema SESI , para o exercício de 2025 (Resolução SESI/CN Nº 0052/2025).</t>
-        </is>
-      </c>
+      <c r="B11" t="inlineStr"/>
       <c r="C11" t="inlineStr">
         <is>
           <t>PREVORC_REC</t>
@@ -3084,7 +3044,7 @@
         </is>
       </c>
       <c r="H11" t="n">
-        <v>55028199.26</v>
+        <v>51186159.12</v>
       </c>
     </row>
     <row r="12">
@@ -3093,11 +3053,7 @@
           <t>Jan - Dez</t>
         </is>
       </c>
-      <c r="B12" t="inlineStr">
-        <is>
-          <t>O Conselho Nacional do Serviço Social da Indústria (SESI), em 28/07/2025, no uso de suas atribuições legais e regulamentares, resolveu aprovar o Plano de Ação e Orçamento Retificado do sistema SESI , para o exercício de 2025 (Resolução SESI/CN Nº 0052/2025).</t>
-        </is>
-      </c>
+      <c r="B12" t="inlineStr"/>
       <c r="C12" t="inlineStr">
         <is>
           <t>PREVORC_REC</t>
@@ -3120,7 +3076,7 @@
         </is>
       </c>
       <c r="H12" t="n">
-        <v>2600000.01</v>
+        <v>1261013.9</v>
       </c>
     </row>
     <row r="13">
@@ -3129,11 +3085,7 @@
           <t>Jan - Dez</t>
         </is>
       </c>
-      <c r="B13" t="inlineStr">
-        <is>
-          <t>O Conselho Nacional do Serviço Social da Indústria (SESI), em 28/07/2025, no uso de suas atribuições legais e regulamentares, resolveu aprovar o Plano de Ação e Orçamento Retificado do sistema SESI , para o exercício de 2025 (Resolução SESI/CN Nº 0052/2025).</t>
-        </is>
-      </c>
+      <c r="B13" t="inlineStr"/>
       <c r="C13" t="inlineStr">
         <is>
           <t>PREVORC_REC</t>
@@ -3156,7 +3108,7 @@
         </is>
       </c>
       <c r="H13" t="n">
-        <v>4344516.22</v>
+        <v>3631305.76</v>
       </c>
     </row>
     <row r="14">
@@ -3165,11 +3117,7 @@
           <t>Jan - Dez</t>
         </is>
       </c>
-      <c r="B14" t="inlineStr">
-        <is>
-          <t>O Conselho Nacional do Serviço Social da Indústria (SESI), em 28/07/2025, no uso de suas atribuições legais e regulamentares, resolveu aprovar o Plano de Ação e Orçamento Retificado do sistema SESI , para o exercício de 2025 (Resolução SESI/CN Nº 0052/2025).</t>
-        </is>
-      </c>
+      <c r="B14" t="inlineStr"/>
       <c r="C14" t="inlineStr">
         <is>
           <t>PREVORC_REC</t>
@@ -3192,7 +3140,7 @@
         </is>
       </c>
       <c r="H14" t="n">
-        <v>936078236.59</v>
+        <v>852160019.27</v>
       </c>
     </row>
     <row r="15">
@@ -3201,11 +3149,7 @@
           <t>Jan - Dez</t>
         </is>
       </c>
-      <c r="B15" t="inlineStr">
-        <is>
-          <t>O Conselho Nacional do Serviço Social da Indústria (SESI), em 28/07/2025, no uso de suas atribuições legais e regulamentares, resolveu aprovar o Plano de Ação e Orçamento Retificado do sistema SESI , para o exercício de 2025 (Resolução SESI/CN Nº 0052/2025).</t>
-        </is>
-      </c>
+      <c r="B15" t="inlineStr"/>
       <c r="C15" t="inlineStr">
         <is>
           <t>PREVORC_REC</t>
@@ -3228,7 +3172,7 @@
         </is>
       </c>
       <c r="H15" t="n">
-        <v>1643014247.64</v>
+        <v>1502330018.11</v>
       </c>
     </row>
     <row r="16">
@@ -3237,11 +3181,7 @@
           <t>Jan - Dez</t>
         </is>
       </c>
-      <c r="B16" t="inlineStr">
-        <is>
-          <t>O Conselho Nacional do Serviço Social da Indústria (SESI), em 28/07/2025, no uso de suas atribuições legais e regulamentares, resolveu aprovar o Plano de Ação e Orçamento Retificado do sistema SESI , para o exercício de 2025 (Resolução SESI/CN Nº 0052/2025).</t>
-        </is>
-      </c>
+      <c r="B16" t="inlineStr"/>
       <c r="C16" t="inlineStr">
         <is>
           <t>PREVORC_REC</t>
@@ -3264,7 +3204,7 @@
         </is>
       </c>
       <c r="H16" t="n">
-        <v>318618561</v>
+        <v>303699826.71</v>
       </c>
     </row>
     <row r="17">
@@ -3273,11 +3213,7 @@
           <t>Jan - Dez</t>
         </is>
       </c>
-      <c r="B17" t="inlineStr">
-        <is>
-          <t>O Conselho Nacional do Serviço Social da Indústria (SESI), em 28/07/2025, no uso de suas atribuições legais e regulamentares, resolveu aprovar o Plano de Ação e Orçamento Retificado do sistema SESI , para o exercício de 2025 (Resolução SESI/CN Nº 0052/2025).</t>
-        </is>
-      </c>
+      <c r="B17" t="inlineStr"/>
       <c r="C17" t="inlineStr">
         <is>
           <t>PREVORC_REC</t>
@@ -3300,7 +3236,7 @@
         </is>
       </c>
       <c r="H17" t="n">
-        <v>4082415.92</v>
+        <v>3125821.89</v>
       </c>
     </row>
     <row r="18">
@@ -3309,11 +3245,7 @@
           <t>Jan - Dez</t>
         </is>
       </c>
-      <c r="B18" t="inlineStr">
-        <is>
-          <t>O Conselho Nacional do Serviço Social da Indústria (SESI), em 28/07/2025, no uso de suas atribuições legais e regulamentares, resolveu aprovar o Plano de Ação e Orçamento Retificado do sistema SESI , para o exercício de 2025 (Resolução SESI/CN Nº 0052/2025).</t>
-        </is>
-      </c>
+      <c r="B18" t="inlineStr"/>
       <c r="C18" t="inlineStr">
         <is>
           <t>PREVORC_REC</t>
@@ -3336,7 +3268,7 @@
         </is>
       </c>
       <c r="H18" t="n">
-        <v>236188966.2</v>
+        <v>310327294.09</v>
       </c>
     </row>
     <row r="19">
@@ -3345,11 +3277,7 @@
           <t>Jan - Dez</t>
         </is>
       </c>
-      <c r="B19" t="inlineStr">
-        <is>
-          <t>O Conselho Nacional do Serviço Social da Indústria (SESI), em 28/07/2025, no uso de suas atribuições legais e regulamentares, resolveu aprovar o Plano de Ação e Orçamento Retificado do sistema SESI , para o exercício de 2025 (Resolução SESI/CN Nº 0052/2025).</t>
-        </is>
-      </c>
+      <c r="B19" t="inlineStr"/>
       <c r="C19" t="inlineStr">
         <is>
           <t>PREVORC_REC</t>
@@ -3372,7 +3300,7 @@
         </is>
       </c>
       <c r="H19" t="n">
-        <v>16490023.17</v>
+        <v>102405177.51</v>
       </c>
     </row>
     <row r="20">
@@ -3381,11 +3309,7 @@
           <t>Jan - Dez</t>
         </is>
       </c>
-      <c r="B20" t="inlineStr">
-        <is>
-          <t>O Conselho Nacional do Serviço Social da Indústria (SESI), em 28/07/2025, no uso de suas atribuições legais e regulamentares, resolveu aprovar o Plano de Ação e Orçamento Retificado do sistema SESI , para o exercício de 2025 (Resolução SESI/CN Nº 0052/2025).</t>
-        </is>
-      </c>
+      <c r="B20" t="inlineStr"/>
       <c r="C20" t="inlineStr">
         <is>
           <t>PREVORC_REC</t>
@@ -3408,7 +3332,7 @@
         </is>
       </c>
       <c r="H20" t="n">
-        <v>1600515.69</v>
+        <v>2115931.57</v>
       </c>
     </row>
     <row r="21">
@@ -3417,11 +3341,7 @@
           <t>Jan - Dez</t>
         </is>
       </c>
-      <c r="B21" t="inlineStr">
-        <is>
-          <t>O Conselho Nacional do Serviço Social da Indústria (SESI), em 28/07/2025, no uso de suas atribuições legais e regulamentares, resolveu aprovar o Plano de Ação e Orçamento Retificado do sistema SESI , para o exercício de 2025 (Resolução SESI/CN Nº 0052/2025).</t>
-        </is>
-      </c>
+      <c r="B21" t="inlineStr"/>
       <c r="C21" t="inlineStr">
         <is>
           <t>PREVORC_REC</t>
@@ -3444,7 +3364,7 @@
         </is>
       </c>
       <c r="H21" t="n">
-        <v>25705229.25</v>
+        <v>38458502.14</v>
       </c>
     </row>
   </sheetData>
@@ -3517,7 +3437,7 @@
       <c r="A2" t="inlineStr"/>
       <c r="B2" t="inlineStr">
         <is>
-          <t>17/02/2025 11:38</t>
+          <t>08/08/2024 16:26</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -3527,7 +3447,7 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>Gestão e Suporte às atividades da Diretoria Corporativa</t>
+          <t>Ações de Educação Treinamento e Desenvolvimento</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -3553,7 +3473,7 @@
       <c r="A3" t="inlineStr"/>
       <c r="B3" t="inlineStr">
         <is>
-          <t>17/02/2025 11:38</t>
+          <t>08/08/2024 16:26</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -3563,25 +3483,25 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>Educação Treinamento e Desenvolvimento</t>
+          <t>Gestão de Pessoal e Encargos - Diretoria Corporativa</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Número de Unidades Operacionais e Postos de Atendimentos que prestam atendimento nos Departamentos Regionais do SESI e SENAI e Sede das Federações e do IEL</t>
+          <t>Estabelecido em documento próprio (Ordem de Serviço Remuneração e Encargos CNI/SESI/SENAI/IEL)</t>
         </is>
       </c>
       <c r="F3" t="n">
-        <v>54.63</v>
+        <v>33</v>
       </c>
       <c r="G3" t="n">
-        <v>42.08</v>
+        <v>33</v>
       </c>
       <c r="H3" t="n">
-        <v>1.71</v>
+        <v>33</v>
       </c>
       <c r="I3" t="n">
-        <v>1.58</v>
+        <v>1</v>
       </c>
       <c r="J3" t="inlineStr"/>
     </row>
@@ -3589,7 +3509,7 @@
       <c r="A4" t="inlineStr"/>
       <c r="B4" t="inlineStr">
         <is>
-          <t>17/02/2025 11:38</t>
+          <t>08/08/2024 16:26</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -3599,25 +3519,25 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>Gestão de Pessoal e Encargos - Diretoria Corporativa</t>
+          <t>Gestão e Suporte às atividades da Diretoria Diretoria Corporativa</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Estabelecido em documento próprio (Ordem de Serviço Remuneração e Encargos CNI/SESI/SENAI/IEL)</t>
+          <t>Número de Unidades Operacionais e Postos de Atendimentos que prestam atendimento nos Departamentos Regionais do SESI e SENAI e Sede das Federações e do IEL</t>
         </is>
       </c>
       <c r="F4" t="n">
-        <v>33</v>
+        <v>54.63</v>
       </c>
       <c r="G4" t="n">
-        <v>33</v>
+        <v>42.08</v>
       </c>
       <c r="H4" t="n">
-        <v>33</v>
+        <v>1.71</v>
       </c>
       <c r="I4" t="n">
-        <v>1</v>
+        <v>1.58</v>
       </c>
       <c r="J4" t="inlineStr"/>
     </row>
@@ -3625,7 +3545,7 @@
       <c r="A5" t="inlineStr"/>
       <c r="B5" t="inlineStr">
         <is>
-          <t>17/02/2025 11:38</t>
+          <t>08/08/2024 16:26</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -3635,7 +3555,7 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>Gestão e Suporte as Atividades - Diretoria de Comunicação</t>
+          <t>Ações de Educação Treinamento e Desenvolvimento</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -3661,7 +3581,7 @@
       <c r="A6" t="inlineStr"/>
       <c r="B6" t="inlineStr">
         <is>
-          <t>17/02/2025 11:38</t>
+          <t>08/08/2024 16:26</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -3671,25 +3591,25 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>Gestão de Pessoal e Encargos - Diretoria de Comunicação</t>
+          <t xml:space="preserve">Comunicação - Diretoria de Educação e Tecnologia </t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Número de Unidades Operacionais e Postos de Atendimentos que prestam atendimento nos Departamentos Regionais do SESI e SENAI e Sede das Federações e do IEL</t>
+          <t>Número de Unidades Operacionais e Postos de Atendimentos que prestam atendimento nos departamentos regionais e núcleos regionais.</t>
         </is>
       </c>
       <c r="F6" t="n">
-        <v>54.63</v>
+        <v>55.58</v>
       </c>
       <c r="G6" t="n">
-        <v>42.08</v>
+        <v>42.81</v>
       </c>
       <c r="H6" t="n">
-        <v>1.71</v>
+        <v>0</v>
       </c>
       <c r="I6" t="n">
-        <v>1.58</v>
+        <v>1.61</v>
       </c>
       <c r="J6" t="inlineStr"/>
     </row>
@@ -3697,7 +3617,7 @@
       <c r="A7" t="inlineStr"/>
       <c r="B7" t="inlineStr">
         <is>
-          <t>17/02/2025 11:38</t>
+          <t>08/08/2024 16:26</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -3707,7 +3627,7 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>Educação Treinamento e Desenvolvimento</t>
+          <t>Comunicação áreas técnicas - Diretoria de Inovação</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -3733,7 +3653,7 @@
       <c r="A8" t="inlineStr"/>
       <c r="B8" t="inlineStr">
         <is>
-          <t>17/02/2025 11:38</t>
+          <t>08/08/2024 16:26</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -3743,7 +3663,7 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>Gestão e Administração - Gerência de Comunicação Integr</t>
+          <t>Gestão de Pessoal e Encargos - Diretoria de Comunicação</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
@@ -3769,7 +3689,7 @@
       <c r="A9" t="inlineStr"/>
       <c r="B9" t="inlineStr">
         <is>
-          <t>17/02/2025 11:38</t>
+          <t>08/08/2024 16:26</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -3779,7 +3699,7 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>Gestão de Pessoal e Encargos - Ger de Comunic. Integrad</t>
+          <t>Gestão e Suporte as Atividades - Diretoria de Comunicação</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
@@ -3805,7 +3725,7 @@
       <c r="A10" t="inlineStr"/>
       <c r="B10" t="inlineStr">
         <is>
-          <t>17/02/2025 11:38</t>
+          <t>08/08/2024 16:26</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -3815,7 +3735,7 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>Gestão de Pessoal e Encargos - Ger Comunic. Interna e E</t>
+          <t>Gestão e Administração - Gerência de Comunicação Integrada, Planej. e Intel</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
@@ -3841,7 +3761,7 @@
       <c r="A11" t="inlineStr"/>
       <c r="B11" t="inlineStr">
         <is>
-          <t>17/02/2025 11:38</t>
+          <t>08/08/2024 16:26</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -3851,7 +3771,7 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>Gestão e Suporte as Atividades - Ger Comunic. Interna</t>
+          <t>Gestão de Pessoal e Encargos - Ger de Comunic. Integrada, Planej. e Inteligência</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
@@ -3877,17 +3797,17 @@
       <c r="A12" t="inlineStr"/>
       <c r="B12" t="inlineStr">
         <is>
-          <t>17/02/2025 11:38</t>
+          <t>08/08/2024 16:26</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Diretoria de Comunicação</t>
+          <t>Diretoria de Inovação</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>Sistematização e Gestão das Info. - Customer Relationship Management (CRM)</t>
+          <t>Educação Treinamento e Desenvolvimento Diretoria de Inovação</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
@@ -3913,35 +3833,35 @@
       <c r="A13" t="inlineStr"/>
       <c r="B13" t="inlineStr">
         <is>
-          <t>17/02/2025 11:38</t>
+          <t>08/08/2024 16:26</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Diretoria de Comunicação</t>
+          <t>Diretoria de Inovação</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>Gestão de Pessoal e Encargos - Super. de Jornalismo</t>
+          <t>Congresso Internacional de Inovação da Indústria - Convênio CNI/SEBRAE - Entidade</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Número de Unidades Operacionais e Postos de Atendimentos que prestam atendimento nos Departamentos Regionais do SESI e SENAI e Sede das Federações e do IEL</t>
+          <t>Estabelecido em Convênio</t>
         </is>
       </c>
       <c r="F13" t="n">
-        <v>54.63</v>
+        <v>53.4</v>
       </c>
       <c r="G13" t="n">
-        <v>42.08</v>
+        <v>41.56</v>
       </c>
       <c r="H13" t="n">
-        <v>1.71</v>
+        <v>0</v>
       </c>
       <c r="I13" t="n">
-        <v>1.58</v>
+        <v>5.04</v>
       </c>
       <c r="J13" t="inlineStr"/>
     </row>
@@ -3949,35 +3869,35 @@
       <c r="A14" t="inlineStr"/>
       <c r="B14" t="inlineStr">
         <is>
-          <t>17/02/2025 11:38</t>
+          <t>08/08/2024 16:26</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Diretoria de Comunicação</t>
+          <t>Diretoria de Inovação</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>Gestão e Administração - Super. de Jornalismo</t>
+          <t>Edição 2023 - Prêmio de Inovação - Convênio CNI/SEBRAE - Entidade</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Número de Unidades Operacionais e Postos de Atendimentos que prestam atendimento nos Departamentos Regionais do SESI e SENAI e Sede das Federações e do IEL</t>
+          <t>Estabelecido em Convênio</t>
         </is>
       </c>
       <c r="F14" t="n">
-        <v>54.63</v>
+        <v>50.55</v>
       </c>
       <c r="G14" t="n">
-        <v>42.08</v>
+        <v>38.71</v>
       </c>
       <c r="H14" t="n">
-        <v>1.71</v>
+        <v>5.7</v>
       </c>
       <c r="I14" t="n">
-        <v>1.58</v>
+        <v>5.04</v>
       </c>
       <c r="J14" t="inlineStr"/>
     </row>
@@ -3985,17 +3905,17 @@
       <c r="A15" t="inlineStr"/>
       <c r="B15" t="inlineStr">
         <is>
-          <t>17/02/2025 11:38</t>
+          <t>08/08/2024 16:26</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Diretoria de Comunicação</t>
+          <t>Diretoria de Inovação</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>Programa de Relacionamento</t>
+          <t>Gestão da Diretoria de Tecnologia e Inovação</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
@@ -4021,17 +3941,17 @@
       <c r="A16" t="inlineStr"/>
       <c r="B16" t="inlineStr">
         <is>
-          <t>17/02/2025 11:38</t>
+          <t>08/08/2024 16:26</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Diretoria de Comunicação</t>
+          <t>Diretoria de Inovação</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>Gestão de Pessoal e Encargos - Ger de Conteúdos Mult</t>
+          <t>Gestão de Pessoal e Encargos - Gerência de Monitoramento e Controle de Projetos</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
@@ -4057,35 +3977,35 @@
       <c r="A17" t="inlineStr"/>
       <c r="B17" t="inlineStr">
         <is>
-          <t>17/02/2025 11:38</t>
+          <t>08/08/2024 16:26</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Diretoria de Comunicação</t>
+          <t>Diretoria de Inovação</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>Gestão de Pessoal e Encargos - Ger de Imprensa</t>
+          <t>Portal e Workshops Mobilização Empresarial pela Inovação (MEI) Tools - Convênio CNI/SEBRAE - Entidade</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Número de Unidades Operacionais e Postos de Atendimentos que prestam atendimento nos Departamentos Regionais do SESI e SENAI e Sede das Federações e do IEL</t>
+          <t>Estabelecido em Convênio</t>
         </is>
       </c>
       <c r="F17" t="n">
-        <v>54.63</v>
+        <v>50.55</v>
       </c>
       <c r="G17" t="n">
-        <v>42.08</v>
+        <v>38.71</v>
       </c>
       <c r="H17" t="n">
-        <v>1.71</v>
+        <v>5.7</v>
       </c>
       <c r="I17" t="n">
-        <v>1.58</v>
+        <v>5.04</v>
       </c>
       <c r="J17" t="inlineStr"/>
     </row>
@@ -4093,17 +4013,17 @@
       <c r="A18" t="inlineStr"/>
       <c r="B18" t="inlineStr">
         <is>
-          <t>17/02/2025 11:38</t>
+          <t>08/08/2024 16:26</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Diretoria de Comunicação</t>
+          <t>Diretoria de Inovação</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>Gestão e Administração - Superintendência de Publicidade</t>
+          <t>Gestão de Pessoal e Encargos - Gerência de Mobilização Empresarial</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
@@ -4129,17 +4049,17 @@
       <c r="A19" t="inlineStr"/>
       <c r="B19" t="inlineStr">
         <is>
-          <t>17/02/2025 11:38</t>
+          <t>08/08/2024 16:26</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Diretoria de Comunicação</t>
+          <t>Diretoria de Inovação</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>Gestão de Pessoal e Encargos - Superintendência de Publicidade</t>
+          <t>Gestão de Pessoal e Encargos - Superintendência de Projetos</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
@@ -4165,17 +4085,17 @@
       <c r="A20" t="inlineStr"/>
       <c r="B20" t="inlineStr">
         <is>
-          <t>17/02/2025 11:38</t>
+          <t>08/08/2024 16:26</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Diretoria de Comunicação</t>
+          <t>Diretoria de Inovação</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>Gestão de Pessoal e Encargos - Ger de Criação de Public</t>
+          <t>Gestão da Superintendência de Projetos de Inovação</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
@@ -4201,17 +4121,17 @@
       <c r="A21" t="inlineStr"/>
       <c r="B21" t="inlineStr">
         <is>
-          <t>17/02/2025 11:38</t>
+          <t>08/08/2024 16:26</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Diretoria de Comunicação</t>
+          <t>Diretoria de Inovação</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>Gestão de Pessoal e Encargos - Ger. de Estratégia de Public</t>
+          <t>Secretaria Executiva da Mobilização Empresarial pela Inovação (MEI)</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
@@ -4297,7 +4217,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>05/02/2026 16:42</t>
+          <t>27/01/2025 09:44</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -4311,10 +4231,10 @@
         </is>
       </c>
       <c r="D2" t="n">
-        <v>237548450.59</v>
+        <v>243605418.66</v>
       </c>
       <c r="E2" t="n">
-        <v>68.86</v>
+        <v>67.47</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -4327,16 +4247,16 @@
         </is>
       </c>
       <c r="H2" t="n">
-        <v>20545455.43</v>
+        <v>53098391.63</v>
       </c>
       <c r="I2" t="n">
-        <v>8.65</v>
+        <v>21.8</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>05/02/2026 16:42</t>
+          <t>27/01/2025 09:44</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -4350,10 +4270,10 @@
         </is>
       </c>
       <c r="D3" t="n">
-        <v>237548450.59</v>
+        <v>243605418.66</v>
       </c>
       <c r="E3" t="n">
-        <v>68.86</v>
+        <v>67.47</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -4366,16 +4286,16 @@
         </is>
       </c>
       <c r="H3" t="n">
-        <v>235166.11</v>
+        <v>762746.49</v>
       </c>
       <c r="I3" t="n">
-        <v>0.1</v>
+        <v>0.31</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>05/02/2026 16:42</t>
+          <t>27/01/2025 09:44</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -4389,10 +4309,10 @@
         </is>
       </c>
       <c r="D4" t="n">
-        <v>237548450.59</v>
+        <v>243605418.66</v>
       </c>
       <c r="E4" t="n">
-        <v>68.86</v>
+        <v>67.47</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -4414,7 +4334,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>05/02/2026 16:42</t>
+          <t>27/01/2025 09:44</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -4428,10 +4348,10 @@
         </is>
       </c>
       <c r="D5" t="n">
-        <v>237548450.59</v>
+        <v>243605418.66</v>
       </c>
       <c r="E5" t="n">
-        <v>68.86</v>
+        <v>67.47</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -4453,7 +4373,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>05/02/2026 16:42</t>
+          <t>27/01/2025 09:44</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -4467,10 +4387,10 @@
         </is>
       </c>
       <c r="D6" t="n">
-        <v>237548450.59</v>
+        <v>243605418.66</v>
       </c>
       <c r="E6" t="n">
-        <v>68.86</v>
+        <v>67.47</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -4483,16 +4403,16 @@
         </is>
       </c>
       <c r="H6" t="n">
-        <v>43723242.2</v>
+        <v>72761431.14</v>
       </c>
       <c r="I6" t="n">
-        <v>18.41</v>
+        <v>29.87</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>05/02/2026 16:42</t>
+          <t>27/01/2025 09:44</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -4506,10 +4426,10 @@
         </is>
       </c>
       <c r="D7" t="n">
-        <v>237548450.59</v>
+        <v>243605418.66</v>
       </c>
       <c r="E7" t="n">
-        <v>68.86</v>
+        <v>67.47</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -4522,16 +4442,16 @@
         </is>
       </c>
       <c r="H7" t="n">
-        <v>96876993.06</v>
+        <v>113449232.23</v>
       </c>
       <c r="I7" t="n">
-        <v>40.78</v>
+        <v>46.57</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>05/02/2026 16:42</t>
+          <t>27/01/2025 09:44</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -4545,10 +4465,10 @@
         </is>
       </c>
       <c r="D8" t="n">
-        <v>237548450.59</v>
+        <v>243605418.66</v>
       </c>
       <c r="E8" t="n">
-        <v>68.86</v>
+        <v>67.47</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -4561,16 +4481,16 @@
         </is>
       </c>
       <c r="H8" t="n">
-        <v>69187716.45999999</v>
+        <v>3533617.17</v>
       </c>
       <c r="I8" t="n">
-        <v>29.13</v>
+        <v>1.45</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>05/02/2026 16:42</t>
+          <t>27/01/2025 09:44</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -4584,10 +4504,10 @@
         </is>
       </c>
       <c r="D9" t="n">
-        <v>237548450.59</v>
+        <v>243605418.66</v>
       </c>
       <c r="E9" t="n">
-        <v>68.86</v>
+        <v>67.47</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -4600,16 +4520,16 @@
         </is>
       </c>
       <c r="H9" t="n">
-        <v>6979877.33</v>
+        <v>0</v>
       </c>
       <c r="I9" t="n">
-        <v>2.94</v>
+        <v>0</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>05/02/2026 16:42</t>
+          <t>27/01/2025 09:44</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -4623,10 +4543,10 @@
         </is>
       </c>
       <c r="D10" t="n">
-        <v>107418441.4</v>
+        <v>117461152.13</v>
       </c>
       <c r="E10" t="n">
-        <v>31.14</v>
+        <v>32.53</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -4639,16 +4559,16 @@
         </is>
       </c>
       <c r="H10" t="n">
-        <v>11870017.05</v>
+        <v>29124270.25</v>
       </c>
       <c r="I10" t="n">
-        <v>11.05</v>
+        <v>24.79</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>05/02/2026 16:42</t>
+          <t>27/01/2025 09:44</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -4662,10 +4582,10 @@
         </is>
       </c>
       <c r="D11" t="n">
-        <v>107418441.4</v>
+        <v>117461152.13</v>
       </c>
       <c r="E11" t="n">
-        <v>31.14</v>
+        <v>32.53</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -4678,16 +4598,16 @@
         </is>
       </c>
       <c r="H11" t="n">
-        <v>26842808.48</v>
+        <v>32743184.62</v>
       </c>
       <c r="I11" t="n">
-        <v>24.99</v>
+        <v>27.88</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>05/02/2026 16:42</t>
+          <t>27/01/2025 09:44</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -4701,10 +4621,10 @@
         </is>
       </c>
       <c r="D12" t="n">
-        <v>107418441.4</v>
+        <v>117461152.13</v>
       </c>
       <c r="E12" t="n">
-        <v>31.14</v>
+        <v>32.53</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -4717,16 +4637,16 @@
         </is>
       </c>
       <c r="H12" t="n">
-        <v>68705615.87</v>
+        <v>55593697.26</v>
       </c>
       <c r="I12" t="n">
-        <v>63.96</v>
+        <v>47.33</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>05/02/2026 16:42</t>
+          <t>27/01/2025 09:44</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -4740,7 +4660,7 @@
         </is>
       </c>
       <c r="D13" t="n">
-        <v>344966891.99</v>
+        <v>361066570.79</v>
       </c>
       <c r="E13" t="n">
         <v>100</v>
@@ -4834,7 +4754,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>22/01/2026 12:31</t>
+          <t>27/01/2025 09:55</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -4854,7 +4774,7 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Valores Aprovados no Plano de Ação Retificado 2025</t>
+          <t>Valores Aprovados no Plano de Ação Retificado 2024</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
@@ -4875,7 +4795,7 @@
         <v>0</v>
       </c>
       <c r="K2" t="n">
-        <v>4539600</v>
+        <v>1487500</v>
       </c>
       <c r="L2" t="n">
         <v>0</v>
@@ -4885,7 +4805,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>22/01/2026 12:31</t>
+          <t>27/01/2025 09:55</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -4905,7 +4825,7 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Valores Aprovados no Plano de Ação Retificado 2025</t>
+          <t>Valores Aprovados no Plano de Ação Retificado 2024</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
@@ -4926,7 +4846,7 @@
         <v>0</v>
       </c>
       <c r="K3" t="n">
-        <v>10592400</v>
+        <v>13790825</v>
       </c>
       <c r="L3" t="n">
         <v>0</v>
@@ -4936,7 +4856,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>22/01/2026 12:31</t>
+          <t>27/01/2025 09:55</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -4956,7 +4876,7 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Valores Aprovados no Plano de Ação Retificado 2025</t>
+          <t>Valores Aprovados no Plano de Ação Retificado 2024</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
@@ -4974,20 +4894,20 @@
         </is>
       </c>
       <c r="J4" t="n">
-        <v>17773571.07</v>
+        <v>80680420.42</v>
       </c>
       <c r="K4" t="n">
-        <v>29389779.59</v>
+        <v>43814864.16</v>
       </c>
       <c r="L4" t="n">
-        <v>165.4</v>
+        <v>54.3</v>
       </c>
       <c r="M4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>22/01/2026 12:31</t>
+          <t>27/01/2025 09:55</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -5007,7 +4927,7 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Valores Aprovados no Plano de Ação Retificado 2025</t>
+          <t>Valores Aprovados no Plano de Ação Retificado 2024</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
@@ -5025,7 +4945,7 @@
         </is>
       </c>
       <c r="J5" t="n">
-        <v>1921000</v>
+        <v>0</v>
       </c>
       <c r="K5" t="n">
         <v>0</v>
@@ -5038,7 +4958,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>22/01/2026 12:31</t>
+          <t>27/01/2025 09:55</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -5058,7 +4978,7 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Valores Aprovados no Plano de Ação Retificado 2025</t>
+          <t>Valores Aprovados no Plano de Ação Retificado 2024</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
@@ -5089,7 +5009,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>22/01/2026 12:31</t>
+          <t>27/01/2025 09:55</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -5109,7 +5029,7 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Valores Aprovados no Plano de Ação Retificado 2025</t>
+          <t>Valores Aprovados no Plano de Ação Retificado 2024</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
@@ -5127,7 +5047,7 @@
         </is>
       </c>
       <c r="J7" t="n">
-        <v>400000</v>
+        <v>0</v>
       </c>
       <c r="K7" t="n">
         <v>0</v>
@@ -5140,7 +5060,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>22/01/2026 12:31</t>
+          <t>27/01/2025 09:55</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -5160,7 +5080,7 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Valores Aprovados no Plano de Ação Retificado 2025</t>
+          <t>Valores Aprovados no Plano de Ação Retificado 2024</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
@@ -5178,13 +5098,13 @@
         </is>
       </c>
       <c r="J8" t="n">
-        <v>20094571.07</v>
+        <v>80680420.42</v>
       </c>
       <c r="K8" t="n">
-        <v>44521779.59</v>
+        <v>59093189.16</v>
       </c>
       <c r="L8" t="n">
-        <v>221.6</v>
+        <v>73.2</v>
       </c>
       <c r="M8" t="inlineStr"/>
     </row>
